--- a/assets/budget.xlsx
+++ b/assets/budget.xlsx
@@ -197,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -415,6 +415,15 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1049,7 +1058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1063,7 +1072,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>งบประมาณ v4 — จ่ายแล้ว + พกไป + เมนูอัปเกรด (แก้ตัวเลขได้)</t>
+          <t>งบประมาณ v4.1 — จ่ายแล้ว + พกไป + เมนูอัปเกรด (แก้ตัวเลขได้ • 1 CNY = 4.95 THB)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1072,6 +1081,13 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>🔧 แก้จาก v4: ① อาหาร ¥800→¥965 ให้ตรงแผนกินจริง (+817 บาท/คน) ② ที่พักใช้ยอดจ่ายจริง 5,726.05 ③ เติมคอลัมน์ % รวม ④ เพิ่มฉาก A/B/C</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -1119,7 +1135,10 @@
       <c r="D4" s="14" t="n">
         <v>9922</v>
       </c>
-      <c r="E4" s="15" t="n"/>
+      <c r="E4" s="74">
+        <f>IF($D$14=0,0,D4/$D$14)</f>
+        <v/>
+      </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
           <t>โลว์คอสต์: ไม่มีอาหารบนเครื่อง • เช็กโควตากระเป๋าโหลด</t>
@@ -1138,16 +1157,18 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1158</v>
-      </c>
-      <c r="D5" s="14">
-        <f>C5*4.95</f>
+        <v>1156.8</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>5726</v>
+      </c>
+      <c r="E5" s="74">
+        <f>IF($D$14=0,0,D5/$D$14)</f>
         <v/>
       </c>
-      <c r="E5" s="15" t="n"/>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>40,082.32 ÷ 7 • ไม่มีอาหารเช้า • เช็กอินถึง 23:30</t>
+          <t>จ่ายจริง 40,082.32 ÷ 7 = 5,726.05 บาท (ปัดเป็น 5,726) • ไม่มีอาหารเช้า • เช็กอินถึง 23:30</t>
         </is>
       </c>
     </row>
@@ -1166,10 +1187,13 @@
         <v>130</v>
       </c>
       <c r="D6" s="20">
-        <f>C6*4.95</f>
+        <f>ROUND(C6*4.95,0)</f>
         <v/>
       </c>
-      <c r="E6" s="21" t="n"/>
+      <c r="E6" s="75">
+        <f>IF($D$14=0,0,D6/$D$14)</f>
+        <v/>
+      </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
           <t>PVG⇄จิ้งอัน ¥200–240/คัน/เที่ยว ×2 คัน ÷7 ×2 เที่ยว</t>
@@ -1191,10 +1215,13 @@
         <v>129</v>
       </c>
       <c r="D7" s="20">
-        <f>C7*4.95</f>
+        <f>ROUND(C7*4.95,0)</f>
         <v/>
       </c>
-      <c r="E7" s="21" t="n"/>
+      <c r="E7" s="75">
+        <f>IF($D$14=0,0,D7/$D$14)</f>
+        <v/>
+      </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
           <t>Metro ¥3–9/เที่ยว (QR Alipay) • แท็กซี่ hop หงโข่ว 1 ครั้ง ¥8/คน • เผื่อ Didi วันฝน</t>
@@ -1216,10 +1243,13 @@
         <v>329</v>
       </c>
       <c r="D8" s="20">
-        <f>C8*4.95</f>
+        <f>ROUND(C8*4.95,0)</f>
         <v/>
       </c>
-      <c r="E8" s="21" t="n"/>
+      <c r="E8" s="75">
+        <f>IF($D$14=0,0,D8/$D$14)</f>
+        <v/>
+      </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
           <t>NatHist ¥30 + Yu Garden ¥30 + Christkindl ¥35 + ดาราศาสตร์ ¥30 + Aquarium ¥122 + เฟอร์รี่ ¥2 + Shikumen ¥20 + ไปรษณีย์ ¥10 + คาเฟ่กิงโกะ ¥40</t>
@@ -1234,20 +1264,23 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>🍜 อาหาร 6 วัน</t>
+          <t>🍜 อาหาร 6 วัน (¥161/วัน)</t>
         </is>
       </c>
       <c r="C9" s="19" t="n">
-        <v>800</v>
+        <v>965</v>
       </c>
       <c r="D9" s="20">
-        <f>C9*4.95</f>
+        <f>ROUND(C9*4.95,0)</f>
         <v/>
       </c>
-      <c r="E9" s="21" t="n"/>
+      <c r="E9" s="75">
+        <f>IF($D$14=0,0,D9/$D$14)</f>
+        <v/>
+      </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>¥133/วัน ≈ 660 บาท/วัน • รวมมื้อพิเศษ 2 (Haidilao เสาร์ + ส่งท้ายจิ้งอัน จันทร์) • ใช้ตู้เย็นสวีทช่วยมื้อเช้า</t>
+          <t>¥161/วัน ตามแผนกินจริงในชีต 6 (เดิมตั้ง ¥133/วัน ซึ่งต่ำกว่าแผน) • รวมมื้อพิเศษ 2 (Haidilao เสาร์ + ส่งท้ายจิ้งอัน จันทร์) • ใช้ตู้เย็นสวีทช่วยมื้อเช้า</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1299,10 @@
       <c r="D10" s="20" t="n">
         <v>900</v>
       </c>
-      <c r="E10" s="21" t="n"/>
+      <c r="E10" s="75">
+        <f>IF($D$14=0,0,D10/$D$14)</f>
+        <v/>
+      </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
           <t>eSIM โรมมิ่ง 6 วัน ~350 + ประกัน ~550</t>
@@ -1288,10 +1324,13 @@
         <v>55</v>
       </c>
       <c r="D11" s="20">
-        <f>C11*4.95</f>
+        <f>ROUND(C11*4.95,0)</f>
         <v/>
       </c>
-      <c r="E11" s="21" t="n"/>
+      <c r="E11" s="75">
+        <f>IF($D$14=0,0,D11/$D$14)</f>
+        <v/>
+      </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
           <t>ไวน์ร้อน ขนม น้ำ • ตลาด Xintiandi/Kerry เข้าฟรี</t>
@@ -1310,7 +1349,10 @@
         <f>SUM(D4:D5)</f>
         <v/>
       </c>
-      <c r="E12" s="15" t="inlineStr"/>
+      <c r="E12" s="74">
+        <f>D12/$D$14</f>
+        <v/>
+      </c>
       <c r="F12" s="15" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -1325,7 +1367,10 @@
         <f>SUM(D6:D11)</f>
         <v/>
       </c>
-      <c r="E13" s="24" t="inlineStr"/>
+      <c r="E13" s="76">
+        <f>D13/$D$14</f>
+        <v/>
+      </c>
       <c r="F13" s="24" t="inlineStr"/>
     </row>
     <row r="14" ht="26" customHeight="1">
@@ -1341,7 +1386,7 @@
         <v/>
       </c>
       <c r="E14" s="29">
-        <f>D14/D14</f>
+        <f>D14/$D$14</f>
         <v/>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
@@ -1491,6 +1536,119 @@
       <c r="A25" s="40" t="inlineStr">
         <is>
           <t>➖ ช่องทางบีบงบถ้าต้องกลับเพดาน 20,000: สวิตช์วันอาทิตย์เป็นเวอร์ชันฟรี (Museum East + Century Park) −¥160 • ตัด Aquarium −¥122 • กิน ¥100/วัน −¥1,000 • แต่ตั๋ว+โรงแรมจริงกินไป 78% ของเพดานแล้ว — เพดานเดิมแทบเป็นไปไม่ได้ถ้ากินอิ่ม</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>🎚️ 3 ฉากเงินพก (ให้กลุ่มโหวต) — ฐาน "ต้องพกไป" จาก D13</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ฉาก</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>พกไป ฿/คน</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>รวมทั้งทริป ฿/คน</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ทั้งกรุ๊ป 7 คน</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>รายละเอียด</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A ประหยัด</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>ROUND(D13-2584,0)</f>
+        <v/>
+      </c>
+      <c r="C29">
+        <f>D12+B29</f>
+        <v/>
+      </c>
+      <c r="D29">
+        <f>C29*7</f>
+        <v/>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ตัด Aquarium −¥122 • สวิตช์อาทิตย์เป็น Museum East+Century Park ฟรี −¥160 • ลดมื้อพิเศษ 2 มื้อ −¥160 • ตัดคาเฟ่กิงโกะ/Huxinting −¥80 = −¥522</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B ตามแผน v4.1 ⭐</t>
+        </is>
+      </c>
+      <c r="B30">
+        <f>D13</f>
+        <v/>
+      </c>
+      <c r="C30">
+        <f>D12+B30</f>
+        <v/>
+      </c>
+      <c r="D30">
+        <f>C30*7</f>
+        <v/>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ตามแผนปัจจุบัน — แนะนำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C สบาย+อัปเกรดครบ</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>ROUND(D13+SUM(D19:D23),0)</f>
+        <v/>
+      </c>
+      <c r="C31">
+        <f>D12+B31</f>
+        <v/>
+      </c>
+      <c r="D31">
+        <f>C31*7</f>
+        <v/>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>B + ล่องเรือ 525 + Greenhouse 594 + Shanghai Tower 891 + นวด 891 + รูฟท็อป 495 = +3,396</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>➖ ช่องทางบีบงบ: ใช้ฉาก A (−2,584 บาท/คน) • แต่ตั๋ว+โรงแรมจ่ายไปแล้ว 15,648 = 64% ของงบ → บีบได้เฉพาะส่วน "พกไป" เท่านั้น</t>
         </is>
       </c>
     </row>
